--- a/table2_reproduction.xlsx
+++ b/table2_reproduction.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,840 +471,1000 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>delays_zurich_transport</t>
+          <t>predict_droughts</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>windspeed_avg</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5465575</t>
+          <t>19300680</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>7588</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9.334110000000001</v>
+        <v>30.542368</v>
       </c>
       <c r="F2" t="n">
-        <v>0.999894722</v>
+        <v>0.999999507</v>
       </c>
       <c r="G2" t="n">
-        <v>0.706124</v>
+        <v>2.774125</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9996001960000001</v>
+        <v>0.981553205</v>
       </c>
       <c r="I2" t="n">
-        <v>0.228335</v>
+        <v>0.786539</v>
       </c>
       <c r="J2" t="n">
-        <v>335153576</v>
+        <v>15578246.18679993</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>delays_zurich_transport</t>
+          <t>predict_droughts</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>temp</t>
+          <t>WS10M</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5465575</t>
+          <t>19300680</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10.133031</v>
+        <v>32.289423</v>
       </c>
       <c r="F3" t="n">
-        <v>0.99980198</v>
+        <v>0.9999999939999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7395659999999999</v>
+        <v>2.803005</v>
       </c>
       <c r="H3" t="n">
-        <v>0.998395485</v>
+        <v>0.999992707</v>
       </c>
       <c r="I3" t="n">
-        <v>0.223134</v>
+        <v>0.678955</v>
       </c>
       <c r="J3" t="n">
-        <v>334662954.9999999</v>
+        <v>15915830.99439867</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>delays_zurich_transport</t>
+          <t>predict_droughts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>stop_id</t>
+          <t>QV2M</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5465575</t>
+          <t>19300680</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>9.968598999999999</v>
+        <v>33.378304</v>
       </c>
       <c r="F4" t="n">
-        <v>0.999982142</v>
+        <v>0.999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.682075</v>
+        <v>2.897074</v>
       </c>
       <c r="H4" t="n">
-        <v>0.976610349</v>
+        <v>0.999988585</v>
       </c>
       <c r="I4" t="n">
-        <v>0.251702</v>
+        <v>0.682929</v>
       </c>
       <c r="J4" t="n">
-        <v>325792384</v>
+        <v>15915738.2471999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>delays_zurich_transport</t>
+          <t>predict_droughts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>T2M_RANGE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5465575</t>
+          <t>19300680</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10.256153</v>
+        <v>31.175358</v>
       </c>
       <c r="F5" t="n">
-        <v>0.999985649</v>
+        <v>0.999999853</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6986059999999999</v>
+        <v>2.703907</v>
       </c>
       <c r="H5" t="n">
-        <v>0.98701741</v>
+        <v>0.978041676</v>
       </c>
       <c r="I5" t="n">
-        <v>0.28718</v>
+        <v>0.717535</v>
       </c>
       <c r="J5" t="n">
-        <v>330024049</v>
+        <v>15514386.44679999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gpu_kernel_performance</t>
+          <t>delays_zurich_transport</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MWG</t>
+          <t>windspeed_avg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5100000</t>
+          <t>5465575</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10.931646</v>
+        <v>9.288106000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.999894722</v>
       </c>
       <c r="G6" t="n">
-        <v>1.527631</v>
+        <v>0.8115250000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.923359661</v>
+        <v>0.9996001960000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.421078</v>
+        <v>0.227087</v>
       </c>
       <c r="J6" t="n">
-        <v>818613159.3600812</v>
+        <v>335153576</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gpu_kernel_performance</t>
+          <t>delays_zurich_transport</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MDIMC</t>
+          <t>temp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5100000</t>
+          <t>5465575</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>143</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>12.382513</v>
+        <v>9.714608999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.99980198</v>
       </c>
       <c r="G7" t="n">
-        <v>1.493729</v>
+        <v>0.739746</v>
       </c>
       <c r="H7" t="n">
-        <v>0.990344461</v>
+        <v>0.998395485</v>
       </c>
       <c r="I7" t="n">
-        <v>0.216499</v>
+        <v>0.224865</v>
       </c>
       <c r="J7" t="n">
-        <v>890893240.9601057</v>
+        <v>334662954.9999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gpu_kernel_performance</t>
+          <t>delays_zurich_transport</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NWG</t>
+          <t>stop_id</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5100000</t>
+          <t>5465575</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>11.861608</v>
+        <v>10.082349</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.999982142</v>
       </c>
       <c r="G8" t="n">
-        <v>1.597971</v>
+        <v>0.652093</v>
       </c>
       <c r="H8" t="n">
-        <v>0.958262338</v>
+        <v>0.976610349</v>
       </c>
       <c r="I8" t="n">
-        <v>0.372228</v>
+        <v>0.258115</v>
       </c>
       <c r="J8" t="n">
-        <v>859338262.7201198</v>
+        <v>325792384</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>diamonds</t>
+          <t>delays_zurich_transport</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>carat</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>53940</t>
+          <t>5465575</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.037145</v>
+        <v>9.390421</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.999985649</v>
       </c>
       <c r="G9" t="n">
-        <v>0.017005</v>
+        <v>0.695796</v>
       </c>
       <c r="H9" t="n">
-        <v>0.619308347</v>
+        <v>0.98701741</v>
       </c>
       <c r="I9" t="n">
-        <v>0.019411</v>
+        <v>0.283344</v>
       </c>
       <c r="J9" t="n">
-        <v>87802482</v>
+        <v>330024049</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>diamonds</t>
+          <t>gpu_kernel_performance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>MWG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>53940</t>
+          <t>5100000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.032511</v>
+        <v>10.411949</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.010559</v>
+        <v>1.550046</v>
       </c>
       <c r="H10" t="n">
-        <v>0.984396694</v>
+        <v>0.923359661</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00607</v>
+        <v>0.437662</v>
       </c>
       <c r="J10" t="n">
-        <v>148530357</v>
+        <v>818613159.3600812</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>diamonds</t>
+          <t>gpu_kernel_performance</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>MDIMC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>53940</t>
+          <t>5100000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.032794</v>
+        <v>11.236559</v>
       </c>
       <c r="F11" t="n">
-        <v>0.999815903</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0125</v>
+        <v>1.541259</v>
       </c>
       <c r="H11" t="n">
-        <v>0.982937091</v>
+        <v>0.990344461</v>
       </c>
       <c r="I11" t="n">
-        <v>0.008521000000000001</v>
+        <v>0.222997</v>
       </c>
       <c r="J11" t="n">
-        <v>148351023</v>
+        <v>890893240.9601057</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>diamonds</t>
+          <t>gpu_kernel_performance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>NWG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>53940</t>
+          <t>5100000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.037629</v>
+        <v>10.529774</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.020952</v>
+        <v>1.625499</v>
       </c>
       <c r="H12" t="n">
-        <v>0.621338822</v>
+        <v>0.958262338</v>
       </c>
       <c r="I12" t="n">
-        <v>0.023622</v>
+        <v>0.37184</v>
       </c>
       <c r="J12" t="n">
-        <v>87971451</v>
+        <v>859338262.7201198</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>house_sales</t>
+          <t>diamonds</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sqft_living</t>
+          <t>carat</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>53940</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.01885</v>
+        <v>0.036718</v>
       </c>
       <c r="F13" t="n">
-        <v>0.999858149</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.012576</v>
+        <v>0.017119</v>
       </c>
       <c r="H13" t="n">
-        <v>0.855240645</v>
+        <v>0.619308347</v>
       </c>
       <c r="I13" t="n">
-        <v>0.007587</v>
+        <v>0.019804</v>
       </c>
       <c r="J13" t="n">
-        <v>3989925792</v>
+        <v>87802482</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>house_sales</t>
+          <t>diamonds</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>zipcode</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>53940</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.014012</v>
+        <v>0.03196</v>
       </c>
       <c r="F14" t="n">
-        <v>0.99968094</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.007427</v>
+        <v>0.010627</v>
       </c>
       <c r="H14" t="n">
-        <v>0.832171242</v>
+        <v>0.984396694</v>
       </c>
       <c r="I14" t="n">
         <v>0.006272</v>
       </c>
       <c r="J14" t="n">
-        <v>3845312848</v>
+        <v>148530357</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>house_sales</t>
+          <t>diamonds</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sqft_above</t>
+          <t>table</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>53940</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>127</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.01774</v>
+        <v>0.0318</v>
       </c>
       <c r="F15" t="n">
-        <v>0.999788571</v>
+        <v>0.999815903</v>
       </c>
       <c r="G15" t="n">
-        <v>0.012431</v>
+        <v>0.01211</v>
       </c>
       <c r="H15" t="n">
-        <v>0.893202379</v>
+        <v>0.982937091</v>
       </c>
       <c r="I15" t="n">
-        <v>0.007171</v>
+        <v>0.008244</v>
       </c>
       <c r="J15" t="n">
-        <v>4197924964</v>
+        <v>148351023</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>wine</t>
+          <t>diamonds</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>fixed acidity</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>53940</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>554</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.001677</v>
+        <v>0.037369</v>
       </c>
       <c r="F16" t="n">
-        <v>0.989180834</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.003372</v>
+        <v>0.014148</v>
       </c>
       <c r="H16" t="n">
-        <v>0.866269626</v>
+        <v>0.621338822</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00013</v>
+        <v>0.021099</v>
       </c>
       <c r="J16" t="n">
-        <v>640</v>
+        <v>87971451</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>wine</t>
+          <t>house_sales</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>density</t>
+          <t>sqft_living</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>21613</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.002749</v>
+        <v>0.018513</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.999858149</v>
       </c>
       <c r="G17" t="n">
-        <v>0.004811</v>
+        <v>0.012353</v>
       </c>
       <c r="H17" t="n">
-        <v>0.709417165</v>
+        <v>0.855240645</v>
       </c>
       <c r="I17" t="n">
-        <v>0.000193</v>
+        <v>0.007633</v>
       </c>
       <c r="J17" t="n">
-        <v>510</v>
+        <v>3989925792</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>wine</t>
+          <t>house_sales</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>volatile acidity</t>
+          <t>zipcode</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>21613</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.001698</v>
+        <v>0.013553</v>
       </c>
       <c r="F18" t="n">
-        <v>0.991539763</v>
+        <v>0.99968094</v>
       </c>
       <c r="G18" t="n">
-        <v>0.002649</v>
+        <v>0.006755</v>
       </c>
       <c r="H18" t="n">
-        <v>0.806718061</v>
+        <v>0.832171242</v>
       </c>
       <c r="I18" t="n">
-        <v>0.000133</v>
+        <v>0.005655</v>
       </c>
       <c r="J18" t="n">
-        <v>586</v>
+        <v>3845312848</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>wine</t>
+          <t>house_sales</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>citric acid</t>
+          <t>sqft_above</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>21613</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>946</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.001473</v>
+        <v>0.018523</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9968553449999999</v>
+        <v>0.999788571</v>
       </c>
       <c r="G19" t="n">
-        <v>0.002288</v>
+        <v>0.010539</v>
       </c>
       <c r="H19" t="n">
-        <v>0.861179027</v>
+        <v>0.893202379</v>
       </c>
       <c r="I19" t="n">
-        <v>0.000118</v>
+        <v>0.007154</v>
       </c>
       <c r="J19" t="n">
-        <v>634</v>
+        <v>4197924964</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>boston</t>
+          <t>wine</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ZN</t>
+          <t>fixed acidity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.001313</v>
+        <v>0.001773</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9991010299999999</v>
+        <v>0.989180834</v>
       </c>
       <c r="G20" t="n">
-        <v>0.004118</v>
+        <v>0.00474</v>
       </c>
       <c r="H20" t="n">
-        <v>0.892628772</v>
+        <v>0.866269626</v>
       </c>
       <c r="I20" t="n">
-        <v>0.000162</v>
+        <v>0.000116</v>
       </c>
       <c r="J20" t="n">
-        <v>2889.6</v>
+        <v>640</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>boston</t>
+          <t>wine</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>INDUS</t>
+          <t>density</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>388</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.001211</v>
+        <v>0.002721</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.003069</v>
+        <v>0.003963</v>
       </c>
       <c r="H21" t="n">
-        <v>0.788635365</v>
+        <v>0.709417165</v>
       </c>
       <c r="I21" t="n">
-        <v>0.000264</v>
+        <v>0.000191</v>
       </c>
       <c r="J21" t="n">
-        <v>2497.9</v>
+        <v>510</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>wine</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>volatile acidity</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1143</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.001519</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.991539763</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.00296</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.806718061</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.000129</v>
+      </c>
+      <c r="J22" t="n">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>wine</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>citric acid</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1143</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.001412</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9968553449999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.002138</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.861179027</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.000109</v>
+      </c>
+      <c r="J23" t="n">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>boston</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ZN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.001494</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9991010299999999</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.004248</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.892628772</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.000161</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2889.6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>boston</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>INDUS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.001242</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.002341</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.788635365</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.000265</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2497.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>boston</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>506</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>412</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>0.002912</v>
-      </c>
-      <c r="F22" t="n">
+      <c r="E26" t="n">
+        <v>0.002877</v>
+      </c>
+      <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G22" t="n">
-        <v>0.004132</v>
-      </c>
-      <c r="H22" t="n">
+      <c r="G26" t="n">
+        <v>0.004869</v>
+      </c>
+      <c r="H26" t="n">
         <v>0.732018476</v>
       </c>
-      <c r="I22" t="n">
-        <v>0.000397</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="I26" t="n">
+        <v>0.000403</v>
+      </c>
+      <c r="J26" t="n">
         <v>2283.7</v>
       </c>
     </row>

--- a/table2_reproduction.xlsx
+++ b/table2_reproduction.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30.542368</v>
+        <v>32.76202</v>
       </c>
       <c r="F2" t="n">
         <v>0.999999507</v>
       </c>
       <c r="G2" t="n">
-        <v>2.774125</v>
+        <v>2.794999</v>
       </c>
       <c r="H2" t="n">
         <v>0.981553205</v>
       </c>
       <c r="I2" t="n">
-        <v>0.786539</v>
+        <v>0.779465</v>
       </c>
       <c r="J2" t="n">
         <v>15578246.18679993</v>
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>32.289423</v>
+        <v>32.54072</v>
       </c>
       <c r="F3" t="n">
         <v>0.9999999939999999</v>
       </c>
       <c r="G3" t="n">
-        <v>2.803005</v>
+        <v>2.756854</v>
       </c>
       <c r="H3" t="n">
         <v>0.999992707</v>
       </c>
       <c r="I3" t="n">
-        <v>0.678955</v>
+        <v>0.662013</v>
       </c>
       <c r="J3" t="n">
         <v>15915830.99439867</v>
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>33.378304</v>
+        <v>33.689877</v>
       </c>
       <c r="F4" t="n">
         <v>0.999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>2.897074</v>
+        <v>2.830399</v>
       </c>
       <c r="H4" t="n">
         <v>0.999988585</v>
       </c>
       <c r="I4" t="n">
-        <v>0.682929</v>
+        <v>0.677614</v>
       </c>
       <c r="J4" t="n">
         <v>15915738.2471999</v>
@@ -610,19 +610,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>31.175358</v>
+        <v>32.314749</v>
       </c>
       <c r="F5" t="n">
         <v>0.999999853</v>
       </c>
       <c r="G5" t="n">
-        <v>2.703907</v>
+        <v>2.776965</v>
       </c>
       <c r="H5" t="n">
         <v>0.978041676</v>
       </c>
       <c r="I5" t="n">
-        <v>0.717535</v>
+        <v>0.720898</v>
       </c>
       <c r="J5" t="n">
         <v>15514386.44679999</v>
@@ -650,19 +650,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9.288106000000001</v>
+        <v>9.079942000000001</v>
       </c>
       <c r="F6" t="n">
         <v>0.999894722</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8115250000000001</v>
+        <v>0.734496</v>
       </c>
       <c r="H6" t="n">
         <v>0.9996001960000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.227087</v>
+        <v>0.222947</v>
       </c>
       <c r="J6" t="n">
         <v>335153576</v>
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9.714608999999999</v>
+        <v>9.111621</v>
       </c>
       <c r="F7" t="n">
         <v>0.99980198</v>
       </c>
       <c r="G7" t="n">
-        <v>0.739746</v>
+        <v>0.664442</v>
       </c>
       <c r="H7" t="n">
         <v>0.998395485</v>
       </c>
       <c r="I7" t="n">
-        <v>0.224865</v>
+        <v>0.22174</v>
       </c>
       <c r="J7" t="n">
         <v>334662954.9999999</v>
@@ -730,19 +730,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.082349</v>
+        <v>9.449009</v>
       </c>
       <c r="F8" t="n">
         <v>0.999982142</v>
       </c>
       <c r="G8" t="n">
-        <v>0.652093</v>
+        <v>0.663987</v>
       </c>
       <c r="H8" t="n">
         <v>0.976610349</v>
       </c>
       <c r="I8" t="n">
-        <v>0.258115</v>
+        <v>0.249104</v>
       </c>
       <c r="J8" t="n">
         <v>325792384</v>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9.390421</v>
+        <v>9.743774</v>
       </c>
       <c r="F9" t="n">
         <v>0.999985649</v>
       </c>
       <c r="G9" t="n">
-        <v>0.695796</v>
+        <v>0.685737</v>
       </c>
       <c r="H9" t="n">
         <v>0.98701741</v>
       </c>
       <c r="I9" t="n">
-        <v>0.283344</v>
+        <v>0.283573</v>
       </c>
       <c r="J9" t="n">
         <v>330024049</v>
@@ -810,19 +810,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.411949</v>
+        <v>10.38699</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1.550046</v>
+        <v>1.533782</v>
       </c>
       <c r="H10" t="n">
         <v>0.923359661</v>
       </c>
       <c r="I10" t="n">
-        <v>0.437662</v>
+        <v>0.421325</v>
       </c>
       <c r="J10" t="n">
         <v>818613159.3600812</v>
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>11.236559</v>
+        <v>11.153248</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1.541259</v>
+        <v>1.519443</v>
       </c>
       <c r="H11" t="n">
         <v>0.990344461</v>
       </c>
       <c r="I11" t="n">
-        <v>0.222997</v>
+        <v>0.227374</v>
       </c>
       <c r="J11" t="n">
         <v>890893240.9601057</v>
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.529774</v>
+        <v>10.909962</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1.625499</v>
+        <v>1.539816</v>
       </c>
       <c r="H12" t="n">
         <v>0.958262338</v>
       </c>
       <c r="I12" t="n">
-        <v>0.37184</v>
+        <v>0.370793</v>
       </c>
       <c r="J12" t="n">
         <v>859338262.7201198</v>
@@ -911,121 +911,121 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>diamonds</t>
+          <t>synthetic_continuous</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>carat</t>
+          <t>cat_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>53940</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.036718</v>
+        <v>1.207977</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.9999987769999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.017119</v>
+        <v>0.140278</v>
       </c>
       <c r="H13" t="n">
-        <v>0.619308347</v>
+        <v>0.999996498</v>
       </c>
       <c r="I13" t="n">
-        <v>0.019804</v>
+        <v>0.27421</v>
       </c>
       <c r="J13" t="n">
-        <v>87802482</v>
+        <v>798414.168064929</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>diamonds</t>
+          <t>synthetic_continuous</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>cat_100</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>53940</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.03196</v>
+        <v>1.186903</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.999989342</v>
       </c>
       <c r="G14" t="n">
-        <v>0.010627</v>
+        <v>0.12863</v>
       </c>
       <c r="H14" t="n">
-        <v>0.984396694</v>
+        <v>0.999962901</v>
       </c>
       <c r="I14" t="n">
-        <v>0.006272</v>
+        <v>0.283451</v>
       </c>
       <c r="J14" t="n">
-        <v>148530357</v>
+        <v>798381.0993244917</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>diamonds</t>
+          <t>synthetic_continuous</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>cat_1000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>53940</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.0318</v>
+        <v>1.226174</v>
       </c>
       <c r="F15" t="n">
-        <v>0.999815903</v>
+        <v>0.99999809</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01211</v>
+        <v>0.123978</v>
       </c>
       <c r="H15" t="n">
-        <v>0.982937091</v>
+        <v>0.999604465</v>
       </c>
       <c r="I15" t="n">
-        <v>0.008244</v>
+        <v>0.31121</v>
       </c>
       <c r="J15" t="n">
-        <v>148351023</v>
+        <v>798028.9542691666</v>
       </c>
     </row>
     <row r="16">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>carat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1046,266 +1046,266 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.037369</v>
+        <v>0.037009</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.014148</v>
+        <v>0.017068</v>
       </c>
       <c r="H16" t="n">
-        <v>0.621338822</v>
+        <v>0.619308347</v>
       </c>
       <c r="I16" t="n">
-        <v>0.021099</v>
+        <v>0.019671</v>
       </c>
       <c r="J16" t="n">
-        <v>87971451</v>
+        <v>87802482</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>house_sales</t>
+          <t>diamonds</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sqft_living</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>53940</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.018513</v>
+        <v>0.032987</v>
       </c>
       <c r="F17" t="n">
-        <v>0.999858149</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0.012353</v>
+        <v>0.011444</v>
       </c>
       <c r="H17" t="n">
-        <v>0.855240645</v>
+        <v>0.984396694</v>
       </c>
       <c r="I17" t="n">
-        <v>0.007633</v>
+        <v>0.006161</v>
       </c>
       <c r="J17" t="n">
-        <v>3989925792</v>
+        <v>148530357</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>house_sales</t>
+          <t>diamonds</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>zipcode</t>
+          <t>table</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>53940</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>127</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.013553</v>
+        <v>0.032051</v>
       </c>
       <c r="F18" t="n">
-        <v>0.99968094</v>
+        <v>0.999815903</v>
       </c>
       <c r="G18" t="n">
-        <v>0.006755</v>
+        <v>0.010458</v>
       </c>
       <c r="H18" t="n">
-        <v>0.832171242</v>
+        <v>0.982937091</v>
       </c>
       <c r="I18" t="n">
-        <v>0.005655</v>
+        <v>0.008263</v>
       </c>
       <c r="J18" t="n">
-        <v>3845312848</v>
+        <v>148351023</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>house_sales</t>
+          <t>diamonds</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sqft_above</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>53940</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>554</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.018523</v>
+        <v>0.037746</v>
       </c>
       <c r="F19" t="n">
-        <v>0.999788571</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.010539</v>
+        <v>0.01555</v>
       </c>
       <c r="H19" t="n">
-        <v>0.893202379</v>
+        <v>0.621338822</v>
       </c>
       <c r="I19" t="n">
-        <v>0.007154</v>
+        <v>0.021332</v>
       </c>
       <c r="J19" t="n">
-        <v>4197924964</v>
+        <v>87971451</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>wine</t>
+          <t>house_sales</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>fixed acidity</t>
+          <t>sqft_living</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>21613</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.001773</v>
+        <v>0.018803</v>
       </c>
       <c r="F20" t="n">
-        <v>0.989180834</v>
+        <v>0.999858149</v>
       </c>
       <c r="G20" t="n">
-        <v>0.00474</v>
+        <v>0.014221</v>
       </c>
       <c r="H20" t="n">
-        <v>0.866269626</v>
+        <v>0.855240645</v>
       </c>
       <c r="I20" t="n">
-        <v>0.000116</v>
+        <v>0.007528</v>
       </c>
       <c r="J20" t="n">
-        <v>640</v>
+        <v>3989925792</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>wine</t>
+          <t>house_sales</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>density</t>
+          <t>zipcode</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>21613</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.002721</v>
+        <v>0.013458</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0.99968094</v>
       </c>
       <c r="G21" t="n">
-        <v>0.003963</v>
+        <v>0.007933000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.709417165</v>
+        <v>0.832171242</v>
       </c>
       <c r="I21" t="n">
-        <v>0.000191</v>
+        <v>0.005609</v>
       </c>
       <c r="J21" t="n">
-        <v>510</v>
+        <v>3845312848</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>wine</t>
+          <t>house_sales</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>volatile acidity</t>
+          <t>sqft_above</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>21613</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>946</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.001519</v>
+        <v>0.017692</v>
       </c>
       <c r="F22" t="n">
-        <v>0.991539763</v>
+        <v>0.999788571</v>
       </c>
       <c r="G22" t="n">
-        <v>0.00296</v>
+        <v>0.011641</v>
       </c>
       <c r="H22" t="n">
-        <v>0.806718061</v>
+        <v>0.893202379</v>
       </c>
       <c r="I22" t="n">
-        <v>0.000129</v>
+        <v>0.007269</v>
       </c>
       <c r="J22" t="n">
-        <v>586</v>
+        <v>4197924964</v>
       </c>
     </row>
     <row r="23">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>citric acid</t>
+          <t>fixed acidity</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1326,145 +1326,265 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.001412</v>
+        <v>0.001649</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9968553449999999</v>
+        <v>0.989180834</v>
       </c>
       <c r="G23" t="n">
-        <v>0.002138</v>
+        <v>0.006136</v>
       </c>
       <c r="H23" t="n">
-        <v>0.861179027</v>
+        <v>0.866269626</v>
       </c>
       <c r="I23" t="n">
-        <v>0.000109</v>
+        <v>0.000119</v>
       </c>
       <c r="J23" t="n">
-        <v>634</v>
+        <v>640</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>boston</t>
+          <t>wine</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ZN</t>
+          <t>density</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>388</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.001494</v>
+        <v>0.002551</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9991010299999999</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.004248</v>
+        <v>0.006412</v>
       </c>
       <c r="H24" t="n">
-        <v>0.892628772</v>
+        <v>0.709417165</v>
       </c>
       <c r="I24" t="n">
-        <v>0.000161</v>
+        <v>0.000189</v>
       </c>
       <c r="J24" t="n">
-        <v>2889.6</v>
+        <v>510</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>boston</t>
+          <t>wine</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>INDUS</t>
+          <t>volatile acidity</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>135</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.001242</v>
+        <v>0.001418</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0.991539763</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002341</v>
+        <v>0.003806</v>
       </c>
       <c r="H25" t="n">
-        <v>0.788635365</v>
+        <v>0.806718061</v>
       </c>
       <c r="I25" t="n">
-        <v>0.000265</v>
+        <v>0.000125</v>
       </c>
       <c r="J25" t="n">
-        <v>2497.9</v>
+        <v>586</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>wine</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>citric acid</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1143</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.001389</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.9968553449999999</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.002072</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.861179027</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.000113</v>
+      </c>
+      <c r="J26" t="n">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>boston</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ZN</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.001296</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.9991010299999999</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.005355</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.892628772</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.000153</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2889.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>boston</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>INDUS</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.001182</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.002758</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.788635365</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.000262</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2497.9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>boston</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>506</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>412</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>0.002877</v>
-      </c>
-      <c r="F26" t="n">
+      <c r="E29" t="n">
+        <v>0.002851</v>
+      </c>
+      <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G26" t="n">
-        <v>0.004869</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="G29" t="n">
+        <v>0.005307</v>
+      </c>
+      <c r="H29" t="n">
         <v>0.732018476</v>
       </c>
-      <c r="I26" t="n">
-        <v>0.000403</v>
-      </c>
-      <c r="J26" t="n">
+      <c r="I29" t="n">
+        <v>0.000395</v>
+      </c>
+      <c r="J29" t="n">
         <v>2283.7</v>
       </c>
     </row>
